--- a/AAII_Financials/Yearly/NET_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NET_YR_FIN.xlsx
@@ -990,7 +990,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6100</v>
+        <v>9000</v>
       </c>
       <c r="E14" s="3">
         <v>15700</v>
@@ -1103,7 +1103,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2369000</v>
+        <v>2366100</v>
       </c>
       <c r="E17" s="3">
         <v>1808700</v>
@@ -1151,7 +1151,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-201100</v>
+        <v>-198200</v>
       </c>
       <c r="E18" s="3">
         <v>-139100</v>
@@ -1267,7 +1267,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-50400</v>
+        <v>-47500</v>
       </c>
       <c r="E21" s="3">
         <v>-34400</v>
